--- a/formshare/tests/resources/forms/form07B.xlsx
+++ b/formshare/tests/resources/forms/form07B.xlsx
@@ -711,7 +711,7 @@
     <t xml:space="preserve">Just a test</t>
   </si>
   <si>
-    <t xml:space="preserve">Justtest</t>
+    <t xml:space="preserve">Justtest_7</t>
   </si>
 </sst>
 </file>
